--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.05869329015576</v>
+        <v>6.347037659650311</v>
       </c>
       <c r="D2" t="n">
-        <v>40.46004200912783</v>
+        <v>6.574756826483272</v>
       </c>
       <c r="E2" t="n">
-        <v>9.34776982552289</v>
+        <v>1.519012596647469</v>
       </c>
       <c r="F2" t="n">
-        <v>9.928115412803011</v>
+        <v>1.613318754580489</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.4164878389476</v>
+        <v>3.155179273828985</v>
       </c>
       <c r="D3" t="n">
-        <v>18.86796226411321</v>
+        <v>3.066043867918396</v>
       </c>
       <c r="E3" t="n">
-        <v>9.34776982552289</v>
+        <v>1.519012596647469</v>
       </c>
       <c r="F3" t="n">
-        <v>9.928115412803011</v>
+        <v>1.613318754580489</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.40773441082058</v>
+        <v>3.316256841758344</v>
       </c>
       <c r="D4" t="n">
-        <v>20.58546437819675</v>
+        <v>3.345137961456973</v>
       </c>
       <c r="E4" t="n">
-        <v>9.34776982552289</v>
+        <v>1.519012596647469</v>
       </c>
       <c r="F4" t="n">
-        <v>9.928115412803011</v>
+        <v>1.613318754580489</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.10602321587445</v>
+        <v>6.192228772579599</v>
       </c>
       <c r="D5" t="n">
-        <v>38.53820850901881</v>
+        <v>6.262458882715556</v>
       </c>
       <c r="E5" t="n">
-        <v>9.34776982552289</v>
+        <v>1.519012596647469</v>
       </c>
       <c r="F5" t="n">
-        <v>9.928115412803011</v>
+        <v>1.613318754580489</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
